--- a/data/trans_dic/P64D$andando_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P64D$andando_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,87; 22,32</t>
+          <t>10,78; 23,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,78; 34,96</t>
+          <t>21,24; 34,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,96; 25,42</t>
+          <t>16,27; 25,43</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,47; 28,7</t>
+          <t>14,28; 28,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,16; 35,97</t>
+          <t>23,08; 35,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,4; 29,16</t>
+          <t>19,35; 29,12</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,45; 32,84</t>
+          <t>18,26; 32,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,41; 49,13</t>
+          <t>34,28; 50,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,3; 38,11</t>
+          <t>26,98; 37,93</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,5; 29,12</t>
+          <t>15,41; 31,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,36; 34,06</t>
+          <t>9,22; 32,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,36; 28,16</t>
+          <t>12,15; 28,65</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,66; 51,61</t>
+          <t>36,07; 51,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,53; 64,08</t>
+          <t>51,0; 63,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,31; 56,11</t>
+          <t>45,55; 55,88</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21,51; 36,38</t>
+          <t>21,5; 36,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,5; 63,04</t>
+          <t>44,55; 62,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,23; 44,67</t>
+          <t>33,0; 43,78</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,43; 13,56</t>
+          <t>6,39; 13,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,04; 28,64</t>
+          <t>19,86; 28,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,71; 19,4</t>
+          <t>13,8; 19,42</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,56; 30,65</t>
+          <t>6,13; 29,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40,17; 51,44</t>
+          <t>40,24; 51,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,74; 37,15</t>
+          <t>12,4; 36,98</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,03; 23,09</t>
+          <t>13,01; 22,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28,65; 37,39</t>
+          <t>28,98; 37,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19,74; 28,52</t>
+          <t>20,19; 28,52</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20885; 42892</t>
+          <t>20719; 44505</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31441; 50462</t>
+          <t>30656; 49463</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57058; 85554</t>
+          <t>54756; 85588</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35544; 70474</t>
+          <t>35075; 69544</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38361; 59584</t>
+          <t>38233; 59266</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79763; 119910</t>
+          <t>79555; 119749</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27426; 48828</t>
+          <t>27144; 47934</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>40376; 59385</t>
+          <t>41430; 60454</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73590; 102731</t>
+          <t>72724; 102226</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24272; 48748</t>
+          <t>25799; 52026</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24220; 88136</t>
+          <t>23868; 84774</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48420; 119996</t>
+          <t>51773; 122108</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>40732; 58956</t>
+          <t>41204; 59208</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>54130; 68642</t>
+          <t>54625; 68481</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100297; 124206</t>
+          <t>100821; 123686</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29058; 49137</t>
+          <t>29033; 49471</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38447; 54468</t>
+          <t>38490; 54008</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73588; 98923</t>
+          <t>73084; 96964</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21507; 45336</t>
+          <t>21343; 44909</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>61458; 87843</t>
+          <t>60922; 87417</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>87890; 124362</t>
+          <t>88433; 124447</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>41217; 192561</t>
+          <t>38537; 187733</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>108886; 139460</t>
+          <t>109087; 138691</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>105616; 334133</t>
+          <t>111547; 332582</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>256105; 453789</t>
+          <t>255714; 451392</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>418556; 546259</t>
+          <t>423386; 541374</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>676360; 977176</t>
+          <t>691675; 977130</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$andando_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P64D$andando_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,78; 23,16</t>
+          <t>11,82; 23,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,24; 34,27</t>
+          <t>21,78; 33,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,27; 25,43</t>
+          <t>17,22; 25,68</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,28; 28,32</t>
+          <t>14,02; 28,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,08; 35,78</t>
+          <t>24,71; 37,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,35; 29,12</t>
+          <t>20,72; 29,96</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,26; 32,24</t>
+          <t>17,91; 31,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,28; 50,02</t>
+          <t>34,1; 49,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,98; 37,93</t>
+          <t>27,64; 37,76</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,41; 31,08</t>
+          <t>15,0; 30,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,22; 32,76</t>
+          <t>27,41; 41,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,15; 28,65</t>
+          <t>22,42; 32,65</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,07; 51,83</t>
+          <t>36,21; 50,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,0; 63,93</t>
+          <t>50,52; 64,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,55; 55,88</t>
+          <t>45,12; 55,27</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21,5; 36,63</t>
+          <t>21,83; 36,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,55; 62,51</t>
+          <t>45,96; 63,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,0; 43,78</t>
+          <t>33,46; 44,67</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,39; 13,44</t>
+          <t>6,6; 13,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,86; 28,5</t>
+          <t>21,05; 29,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,8; 19,42</t>
+          <t>14,56; 20,18</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,13; 29,88</t>
+          <t>24,62; 34,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40,24; 51,16</t>
+          <t>39,52; 49,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,4; 36,98</t>
+          <t>32,24; 39,44</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,01; 22,96</t>
+          <t>20,65; 24,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28,98; 37,06</t>
+          <t>34,48; 38,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20,19; 28,52</t>
+          <t>27,34; 30,33</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31046</t>
+          <t>33885</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39295</t>
+          <t>41370</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70341</t>
+          <t>75255</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20719; 44505</t>
+          <t>23704; 47853</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30656; 49463</t>
+          <t>33268; 50588</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54756; 85588</t>
+          <t>60837; 90719</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>49981</t>
+          <t>54276</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>48658</t>
+          <t>52739</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98639</t>
+          <t>107015</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35075; 69544</t>
+          <t>35694; 71898</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38233; 59266</t>
+          <t>42882; 64221</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79555; 119749</t>
+          <t>88696; 128287</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36679</t>
+          <t>36281</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50176</t>
+          <t>51890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86855</t>
+          <t>88171</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27144; 47934</t>
+          <t>26795; 46796</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41430; 60454</t>
+          <t>41953; 61253</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72724; 102226</t>
+          <t>75369; 102949</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>35854</t>
+          <t>44980</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>53865</t>
+          <t>61211</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89719</t>
+          <t>106191</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25799; 52026</t>
+          <t>31477; 63697</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23868; 84774</t>
+          <t>49651; 75086</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51773; 122108</t>
+          <t>87678; 127648</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>50216</t>
+          <t>58734</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>61878</t>
+          <t>68873</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112094</t>
+          <t>127607</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>41204; 59208</t>
+          <t>49300; 69175</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>54625; 68481</t>
+          <t>60340; 76675</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100821; 123686</t>
+          <t>115327; 141264</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>38928</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>46510</t>
+          <t>47542</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85095</t>
+          <t>86470</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29033; 49471</t>
+          <t>29709; 49140</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38490; 54008</t>
+          <t>40150; 55315</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73084; 96964</t>
+          <t>74771; 99817</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>31948</t>
+          <t>39044</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>73081</t>
+          <t>90429</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>105029</t>
+          <t>129472</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21343; 44909</t>
+          <t>25569; 53260</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>60922; 87417</t>
+          <t>76181; 105137</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>88433; 124447</t>
+          <t>109100; 151194</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>109707</t>
+          <t>133197</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>124464</t>
+          <t>140876</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>234171</t>
+          <t>274073</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>38537; 187733</t>
+          <t>112012; 154965</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>109087; 138691</t>
+          <t>123382; 155989</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>111547; 332582</t>
+          <t>247310; 302517</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>384014</t>
+          <t>439326</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>497928</t>
+          <t>554929</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>881942</t>
+          <t>994255</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>255714; 451392</t>
+          <t>398335; 480334</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>423386; 541374</t>
+          <t>521053; 587603</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>691675; 977130</t>
+          <t>940498; 1043525</t>
         </is>
       </c>
     </row>
